--- a/backend/wp_templates/K/K6 持有待售资产和负债.xlsx
+++ b/backend/wp_templates/K/K6 持有待售资产和负债.xlsx
@@ -12670,7 +12670,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="173">
-        <f>'明细表K6-2'!L12</f>
+        <f>SUM(E9:E11)</f>
         <v>0</v>
       </c>
       <c r="F8" s="173"/>
@@ -12694,7 +12694,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="173">
-        <f>'明细表K6-2'!L13</f>
+        <f>'明细表K6-2'!L12</f>
         <v>0</v>
       </c>
       <c r="F9" s="173"/>
@@ -12718,7 +12718,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="173">
-        <f>'明细表K6-2'!L14</f>
+        <f>'明细表K6-2'!L13</f>
         <v>0</v>
       </c>
       <c r="F10" s="173"/>
@@ -12742,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="173">
-        <f>'明细表K6-2'!L15</f>
+        <f>'明细表K6-2'!L14</f>
         <v>0</v>
       </c>
       <c r="F11" s="173"/>
